--- a/data/trans_orig/Q64D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q64D_R-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de minutos que utilizan en todos sus desplazamientos para ir a trabajar</t>
+          <t>Número medio de minutos que utilizan en todos sus desplazamientos para ir a trabajar (tasa de respuesta: 88,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,3; 16,61</t>
+          <t>9,42; 16,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,49; 13,95</t>
+          <t>7,52; 13,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,63; 15,58</t>
+          <t>8,71; 15,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,81; 19,4</t>
+          <t>12,28; 20,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 13,97</t>
+          <t>7,69; 14,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,08; 18,8</t>
+          <t>9,96; 18,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,17; 20,72</t>
+          <t>9,98; 20,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,97; 21,27</t>
+          <t>14,2; 21,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 14,33</t>
+          <t>9,46; 14,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,39; 14,42</t>
+          <t>9,26; 14,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,33; 16,13</t>
+          <t>10,27; 15,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,0; 19,69</t>
+          <t>13,81; 19,39</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 13,33</t>
+          <t>7,14; 13,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,75</t>
+          <t>5,4; 10,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,13; 22,22</t>
+          <t>9,83; 22,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,6; 25,17</t>
+          <t>15,61; 25,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,56; 10,7</t>
+          <t>5,71; 10,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,1; 11,05</t>
+          <t>4,9; 10,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,24; 17,22</t>
+          <t>9,8; 16,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,55; 21,18</t>
+          <t>13,53; 20,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,93</t>
+          <t>7,02; 11,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,58</t>
+          <t>5,98; 9,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,23; 18,1</t>
+          <t>11,13; 17,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,35; 21,49</t>
+          <t>15,48; 21,45</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 15,09</t>
+          <t>8,95; 15,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,77</t>
+          <t>6,17; 11,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 10,72</t>
+          <t>5,32; 10,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 17,4</t>
+          <t>1,74; 17,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 10,9</t>
+          <t>2,85; 11,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 9,18</t>
+          <t>4,24; 9,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 11,13</t>
+          <t>3,88; 11,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 12,03</t>
+          <t>4,68; 11,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 14,03</t>
+          <t>8,38; 14,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 10,0</t>
+          <t>6,07; 9,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 10,2</t>
+          <t>5,52; 10,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 14,79</t>
+          <t>1,95; 14,96</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,57; 12,49</t>
+          <t>6,57; 11,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 12,47</t>
+          <t>7,06; 12,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 11,29</t>
+          <t>7,02; 11,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,85; 23,23</t>
+          <t>16,29; 23,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,43</t>
+          <t>4,45; 7,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 8,1</t>
+          <t>4,86; 8,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,67</t>
+          <t>5,65; 9,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,68; 18,52</t>
+          <t>11,91; 18,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,69</t>
+          <t>6,21; 9,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,76</t>
+          <t>6,51; 10,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 9,97</t>
+          <t>6,92; 9,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 20,12</t>
+          <t>14,97; 20,08</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 11,99</t>
+          <t>6,37; 12,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 16,11</t>
+          <t>5,25; 15,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 12,42</t>
+          <t>5,55; 12,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,27; 23,77</t>
+          <t>14,09; 24,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,35; 16,8</t>
+          <t>9,35; 16,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,18; 12,92</t>
+          <t>6,24; 13,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,96; 14,29</t>
+          <t>6,78; 13,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 21,88</t>
+          <t>7,4; 22,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,82; 13,44</t>
+          <t>8,71; 13,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 12,03</t>
+          <t>6,49; 12,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,71</t>
+          <t>6,94; 12,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,85; 21,15</t>
+          <t>9,95; 20,81</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1348,62 +1348,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,0</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,92</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,99</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,25</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,56</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,39</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,34</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,39</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,48</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,7</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,14</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,31</t>
         </is>
       </c>
     </row>
@@ -1416,221 +1416,80 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,84; 11,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,7; 10,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,67; 11,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,12; 18,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,29; 9,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,23; 9,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,9; 11,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,53; 17,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,62; 10,62</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,85; 9,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,07; 11,22</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,03; 17,4</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>10,0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8,92</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9,99</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15,25</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,56</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,39</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,34</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15,39</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9,48</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>8,7</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>10,14</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>15,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>8,8; 11,45</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>7,65; 10,43</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>8,55; 11,4</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8,29; 18,54</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7,39; 9,9</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,25; 9,98</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,8; 12,14</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>12,48; 17,7</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>8,57; 10,66</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>7,72; 9,69</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>9,18; 11,25</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>11,38; 17,34</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>

--- a/data/trans_orig/Q64D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q64D_R-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,55</t>
+          <t>15,36</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,43</t>
+          <t>18,04</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,45</t>
+          <t>16,64</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 16,35</t>
+          <t>9,44; 16,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,52; 13,85</t>
+          <t>7,5; 13,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,71; 15,07</t>
+          <t>8,92; 15,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 20,0</t>
+          <t>11,96; 19,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,69; 14,0</t>
+          <t>7,68; 13,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,96; 18,28</t>
+          <t>10,06; 19,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 20,5</t>
+          <t>10,41; 20,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,2; 21,49</t>
+          <t>14,68; 22,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 14,25</t>
+          <t>9,21; 14,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 14,26</t>
+          <t>9,16; 14,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,27; 15,93</t>
+          <t>10,16; 15,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,81; 19,39</t>
+          <t>14,15; 19,7</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,54</t>
+          <t>20,6</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,92</t>
+          <t>17,33</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,34</t>
+          <t>19,07</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 13,47</t>
+          <t>7,18; 13,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 10,74</t>
+          <t>5,38; 10,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,83; 22,16</t>
+          <t>9,81; 21,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,61; 25,11</t>
+          <t>16,18; 25,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 10,89</t>
+          <t>5,67; 10,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 10,76</t>
+          <t>5,14; 11,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,8; 16,84</t>
+          <t>10,26; 17,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,53; 20,85</t>
+          <t>13,9; 21,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 11,21</t>
+          <t>7,15; 11,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 9,77</t>
+          <t>5,95; 9,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,13; 17,93</t>
+          <t>10,94; 18,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,48; 21,45</t>
+          <t>15,96; 22,07</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,82</t>
+          <t>16,92</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,54</t>
+          <t>7,19</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,91</t>
+          <t>14,41</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,95; 15,49</t>
+          <t>9,08; 15,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,17; 11,5</t>
+          <t>6,12; 11,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 10,87</t>
+          <t>5,21; 10,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 17,26</t>
+          <t>13,03; 21,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,03</t>
+          <t>2,89; 10,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 9,32</t>
+          <t>4,27; 9,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 11,64</t>
+          <t>3,58; 11,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 11,85</t>
+          <t>4,49; 11,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,38; 14,12</t>
+          <t>8,36; 14,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,96</t>
+          <t>6,04; 10,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 10,09</t>
+          <t>5,41; 10,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 14,96</t>
+          <t>11,28; 18,06</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,58</t>
+          <t>19,06</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,4</t>
+          <t>14,66</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,2</t>
+          <t>17,04</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,57; 11,53</t>
+          <t>6,63; 11,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,52 +1146,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 11,52</t>
+          <t>6,77; 11,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,29; 23,76</t>
+          <t>16,11; 22,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,66</t>
+          <t>4,28; 7,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,32</t>
+          <t>4,91; 8,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,73</t>
+          <t>5,66; 9,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,91; 18,33</t>
+          <t>11,84; 18,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,84</t>
+          <t>6,22; 10,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,0</t>
+          <t>6,46; 9,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 9,71</t>
+          <t>6,89; 9,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,97; 20,08</t>
+          <t>14,92; 19,48</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,53</t>
+          <t>17,12</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,31</t>
+          <t>18,87</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,48</t>
+          <t>18,0</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 12,52</t>
+          <t>6,34; 12,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 15,25</t>
+          <t>5,3; 14,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,55; 12,08</t>
+          <t>5,46; 12,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,09; 24,32</t>
+          <t>13,42; 21,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,35; 16,36</t>
+          <t>9,37; 16,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 13,44</t>
+          <t>6,32; 13,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 13,82</t>
+          <t>6,78; 13,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 22,27</t>
+          <t>15,47; 22,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,71; 13,28</t>
+          <t>8,5; 13,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 12,42</t>
+          <t>6,47; 12,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 12,02</t>
+          <t>6,86; 11,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,95; 20,81</t>
+          <t>15,37; 21,26</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,25</t>
+          <t>17,94</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,39</t>
+          <t>16,36</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,31</t>
+          <t>17,23</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,84; 11,7</t>
+          <t>8,77; 11,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,7; 10,39</t>
+          <t>7,66; 10,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,72</t>
+          <t>8,71; 11,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,12; 18,72</t>
+          <t>16,2; 19,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,89</t>
+          <t>7,32; 9,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,23; 9,88</t>
+          <t>7,17; 10,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,9; 11,96</t>
+          <t>8,89; 12,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,53; 17,68</t>
+          <t>14,89; 18,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,62; 10,62</t>
+          <t>8,64; 10,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,85; 9,75</t>
+          <t>7,86; 9,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,07; 11,22</t>
+          <t>9,22; 11,44</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,03; 17,4</t>
+          <t>16,01; 18,57</t>
         </is>
       </c>
     </row>
